--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875881</v>
+        <v>119875883</v>
       </c>
       <c r="B2" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466957</v>
+        <v>466913</v>
       </c>
       <c r="R2" t="n">
-        <v>7052983</v>
+        <v>7053084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875851</v>
+        <v>119875873</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466560</v>
+        <v>467027</v>
       </c>
       <c r="R3" t="n">
-        <v>7052410</v>
+        <v>7053077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875888</v>
+        <v>119875843</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466964</v>
+        <v>466592</v>
       </c>
       <c r="R4" t="n">
-        <v>7052880</v>
+        <v>7052756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875850</v>
+        <v>119875858</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466550</v>
+        <v>466703</v>
       </c>
       <c r="R5" t="n">
-        <v>7052713</v>
+        <v>7052775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875857</v>
+        <v>119875851</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466724</v>
+        <v>466560</v>
       </c>
       <c r="R6" t="n">
-        <v>7052631</v>
+        <v>7052410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875884</v>
+        <v>119875872</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466925</v>
+        <v>466957</v>
       </c>
       <c r="R7" t="n">
-        <v>7052870</v>
+        <v>7053019</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875845</v>
+        <v>119875888</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466588</v>
+        <v>466964</v>
       </c>
       <c r="R8" t="n">
-        <v>7052753</v>
+        <v>7052880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875886</v>
+        <v>119875837</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467236</v>
+        <v>467009</v>
       </c>
       <c r="R9" t="n">
-        <v>7053192</v>
+        <v>7053107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875872</v>
+        <v>119875884</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466957</v>
+        <v>466925</v>
       </c>
       <c r="R10" t="n">
-        <v>7053019</v>
+        <v>7052870</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875846</v>
+        <v>119875836</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466598</v>
+        <v>466991</v>
       </c>
       <c r="R11" t="n">
-        <v>7052725</v>
+        <v>7053264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875840</v>
+        <v>119875876</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466845</v>
+        <v>467110</v>
       </c>
       <c r="R12" t="n">
-        <v>7053062</v>
+        <v>7053045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875834</v>
+        <v>119875859</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467034</v>
+        <v>466682</v>
       </c>
       <c r="R13" t="n">
-        <v>7053239</v>
+        <v>7052885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875882</v>
+        <v>119875875</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466607</v>
+        <v>467073</v>
       </c>
       <c r="R14" t="n">
-        <v>7052792</v>
+        <v>7053067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875841</v>
+        <v>119875856</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2081,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466645</v>
+        <v>466627</v>
       </c>
       <c r="R15" t="n">
-        <v>7052824</v>
+        <v>7052535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875856</v>
+        <v>119875839</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2188,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466627</v>
+        <v>466865</v>
       </c>
       <c r="R16" t="n">
-        <v>7052535</v>
+        <v>7053104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875847</v>
+        <v>119875844</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2295,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466586</v>
+        <v>466581</v>
       </c>
       <c r="R17" t="n">
-        <v>7052711</v>
+        <v>7052764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875849</v>
+        <v>119875862</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2402,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466577</v>
+        <v>466963</v>
       </c>
       <c r="R18" t="n">
-        <v>7052711</v>
+        <v>7052872</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875844</v>
+        <v>119875886</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466581</v>
+        <v>467236</v>
       </c>
       <c r="R19" t="n">
-        <v>7052764</v>
+        <v>7053192</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2555,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875842</v>
+        <v>119875849</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2616,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466632</v>
+        <v>466577</v>
       </c>
       <c r="R20" t="n">
-        <v>7052782</v>
+        <v>7052711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875875</v>
+        <v>119875889</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2699,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467073</v>
+        <v>466941</v>
       </c>
       <c r="R21" t="n">
-        <v>7053067</v>
+        <v>7053004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2764,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875889</v>
+        <v>119875857</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466941</v>
+        <v>466724</v>
       </c>
       <c r="R22" t="n">
-        <v>7053004</v>
+        <v>7052631</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,6 +2866,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875876</v>
+        <v>119875845</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467110</v>
+        <v>466588</v>
       </c>
       <c r="R23" t="n">
-        <v>7053045</v>
+        <v>7052753</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +2977,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875861</v>
+        <v>119875860</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466702</v>
+        <v>466695</v>
       </c>
       <c r="R24" t="n">
-        <v>7052891</v>
+        <v>7052889</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875862</v>
+        <v>119875838</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466963</v>
+        <v>466996</v>
       </c>
       <c r="R25" t="n">
-        <v>7052872</v>
+        <v>7053101</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875837</v>
+        <v>119875846</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3253,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467009</v>
+        <v>466598</v>
       </c>
       <c r="R26" t="n">
-        <v>7053107</v>
+        <v>7052725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3325,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875848</v>
+        <v>119875842</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466583</v>
+        <v>466632</v>
       </c>
       <c r="R27" t="n">
-        <v>7052712</v>
+        <v>7052782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875838</v>
+        <v>119875834</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466996</v>
+        <v>467034</v>
       </c>
       <c r="R28" t="n">
-        <v>7053101</v>
+        <v>7053239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875839</v>
+        <v>119875848</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466865</v>
+        <v>466583</v>
       </c>
       <c r="R29" t="n">
-        <v>7053104</v>
+        <v>7052712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3619,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875836</v>
+        <v>119875847</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466991</v>
+        <v>466586</v>
       </c>
       <c r="R30" t="n">
-        <v>7053264</v>
+        <v>7052711</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875853</v>
+        <v>119875841</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466574</v>
+        <v>466645</v>
       </c>
       <c r="R31" t="n">
-        <v>7052415</v>
+        <v>7052824</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875860</v>
+        <v>119875853</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466695</v>
+        <v>466574</v>
       </c>
       <c r="R32" t="n">
-        <v>7052889</v>
+        <v>7052415</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875874</v>
+        <v>119875835</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4002,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467066</v>
+        <v>467021</v>
       </c>
       <c r="R33" t="n">
-        <v>7053063</v>
+        <v>7053255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875858</v>
+        <v>119875850</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4109,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466703</v>
+        <v>466550</v>
       </c>
       <c r="R34" t="n">
-        <v>7052775</v>
+        <v>7052713</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,7 +4181,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875859</v>
+        <v>119875861</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4216,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466682</v>
+        <v>466702</v>
       </c>
       <c r="R35" t="n">
-        <v>7052885</v>
+        <v>7052891</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4261,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875852</v>
+        <v>119875882</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466560</v>
+        <v>466607</v>
       </c>
       <c r="R36" t="n">
-        <v>7052408</v>
+        <v>7052792</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4359,11 +4364,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875843</v>
+        <v>119875881</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4406,21 +4406,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466592</v>
+        <v>466957</v>
       </c>
       <c r="R37" t="n">
-        <v>7052756</v>
+        <v>7052983</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4466,11 +4466,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4497,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875835</v>
+        <v>119875840</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4537,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467021</v>
+        <v>466845</v>
       </c>
       <c r="R38" t="n">
-        <v>7053255</v>
+        <v>7053062</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4604,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875883</v>
+        <v>119875852</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466913</v>
+        <v>466560</v>
       </c>
       <c r="R39" t="n">
-        <v>7053084</v>
+        <v>7052408</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,6 +4675,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875873</v>
+        <v>119875874</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467027</v>
+        <v>467066</v>
       </c>
       <c r="R40" t="n">
-        <v>7053077</v>
+        <v>7053063</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875889</v>
+        <v>119875845</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466941</v>
+        <v>466588</v>
       </c>
       <c r="R21" t="n">
-        <v>7053004</v>
+        <v>7052753</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,6 +2764,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875845</v>
+        <v>119875889</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466588</v>
+        <v>466941</v>
       </c>
       <c r="R23" t="n">
-        <v>7052753</v>
+        <v>7053004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,11 +2978,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875883</v>
+        <v>119875886</v>
       </c>
       <c r="B2" t="n">
         <v>90580</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466913</v>
+        <v>467236</v>
       </c>
       <c r="R2" t="n">
-        <v>7053084</v>
+        <v>7053192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875873</v>
+        <v>119875888</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467027</v>
+        <v>466964</v>
       </c>
       <c r="R3" t="n">
-        <v>7053077</v>
+        <v>7052880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875843</v>
+        <v>119875852</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466592</v>
+        <v>466560</v>
       </c>
       <c r="R4" t="n">
-        <v>7052756</v>
+        <v>7052408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875858</v>
+        <v>119875881</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466703</v>
+        <v>466957</v>
       </c>
       <c r="R5" t="n">
-        <v>7052775</v>
+        <v>7052983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875851</v>
+        <v>119875884</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466560</v>
+        <v>466925</v>
       </c>
       <c r="R6" t="n">
-        <v>7052410</v>
+        <v>7052870</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875872</v>
+        <v>119875860</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466957</v>
+        <v>466695</v>
       </c>
       <c r="R7" t="n">
-        <v>7053019</v>
+        <v>7052889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875888</v>
+        <v>119875862</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466964</v>
+        <v>466963</v>
       </c>
       <c r="R8" t="n">
-        <v>7052880</v>
+        <v>7052872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875837</v>
+        <v>119875841</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467009</v>
+        <v>466645</v>
       </c>
       <c r="R9" t="n">
-        <v>7053107</v>
+        <v>7052824</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875884</v>
+        <v>119875850</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466925</v>
+        <v>466550</v>
       </c>
       <c r="R10" t="n">
-        <v>7052870</v>
+        <v>7052713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875836</v>
+        <v>119875883</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466991</v>
+        <v>466913</v>
       </c>
       <c r="R11" t="n">
-        <v>7053264</v>
+        <v>7053084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875859</v>
+        <v>119875837</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1877,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466682</v>
+        <v>467009</v>
       </c>
       <c r="R13" t="n">
-        <v>7052885</v>
+        <v>7053107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1907,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875875</v>
+        <v>119875856</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467073</v>
+        <v>466627</v>
       </c>
       <c r="R14" t="n">
-        <v>7053067</v>
+        <v>7052535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875856</v>
+        <v>119875844</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2091,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466627</v>
+        <v>466581</v>
       </c>
       <c r="R15" t="n">
-        <v>7052535</v>
+        <v>7052764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875839</v>
+        <v>119875851</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2198,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466865</v>
+        <v>466560</v>
       </c>
       <c r="R16" t="n">
-        <v>7053104</v>
+        <v>7052410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875844</v>
+        <v>119875842</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2305,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466581</v>
+        <v>466632</v>
       </c>
       <c r="R17" t="n">
-        <v>7052764</v>
+        <v>7052782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875862</v>
+        <v>119875857</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2412,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466963</v>
+        <v>466724</v>
       </c>
       <c r="R18" t="n">
-        <v>7052872</v>
+        <v>7052631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875886</v>
+        <v>119875861</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467236</v>
+        <v>466702</v>
       </c>
       <c r="R19" t="n">
-        <v>7053192</v>
+        <v>7052891</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875849</v>
+        <v>119875845</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2621,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466577</v>
+        <v>466588</v>
       </c>
       <c r="R20" t="n">
-        <v>7052711</v>
+        <v>7052753</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875845</v>
+        <v>119875846</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2728,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466588</v>
+        <v>466598</v>
       </c>
       <c r="R21" t="n">
-        <v>7052753</v>
+        <v>7052725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875857</v>
+        <v>119875848</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2835,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466724</v>
+        <v>466583</v>
       </c>
       <c r="R22" t="n">
-        <v>7052631</v>
+        <v>7052712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875889</v>
+        <v>119875873</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466941</v>
+        <v>467027</v>
       </c>
       <c r="R23" t="n">
-        <v>7053004</v>
+        <v>7053077</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,6 +2973,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875860</v>
+        <v>119875849</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466695</v>
+        <v>466577</v>
       </c>
       <c r="R24" t="n">
-        <v>7052889</v>
+        <v>7052711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875838</v>
+        <v>119875874</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466996</v>
+        <v>467066</v>
       </c>
       <c r="R25" t="n">
-        <v>7053101</v>
+        <v>7053063</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875846</v>
+        <v>119875882</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466598</v>
+        <v>466607</v>
       </c>
       <c r="R26" t="n">
-        <v>7052725</v>
+        <v>7052792</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875842</v>
+        <v>119875843</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466632</v>
+        <v>466592</v>
       </c>
       <c r="R27" t="n">
-        <v>7052782</v>
+        <v>7052756</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3432,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875834</v>
+        <v>119875840</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467034</v>
+        <v>466845</v>
       </c>
       <c r="R28" t="n">
-        <v>7053239</v>
+        <v>7053062</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875848</v>
+        <v>119875858</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3579,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466583</v>
+        <v>466703</v>
       </c>
       <c r="R29" t="n">
-        <v>7052712</v>
+        <v>7052775</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3646,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875847</v>
+        <v>119875872</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3686,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466586</v>
+        <v>466957</v>
       </c>
       <c r="R30" t="n">
-        <v>7052711</v>
+        <v>7053019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875841</v>
+        <v>119875853</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466645</v>
+        <v>466574</v>
       </c>
       <c r="R31" t="n">
-        <v>7052824</v>
+        <v>7052415</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3828,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875853</v>
+        <v>119875859</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466574</v>
+        <v>466682</v>
       </c>
       <c r="R32" t="n">
-        <v>7052415</v>
+        <v>7052885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875835</v>
+        <v>119875889</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467021</v>
+        <v>466941</v>
       </c>
       <c r="R33" t="n">
-        <v>7053255</v>
+        <v>7053004</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,11 +4038,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875850</v>
+        <v>119875836</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4114,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466550</v>
+        <v>466991</v>
       </c>
       <c r="R34" t="n">
-        <v>7052713</v>
+        <v>7053264</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875861</v>
+        <v>119875834</v>
       </c>
       <c r="B35" t="n">
         <v>57310</v>
@@ -4221,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466702</v>
+        <v>467034</v>
       </c>
       <c r="R35" t="n">
-        <v>7052891</v>
+        <v>7053239</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4288,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875882</v>
+        <v>119875838</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466607</v>
+        <v>466996</v>
       </c>
       <c r="R36" t="n">
-        <v>7052792</v>
+        <v>7053101</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,6 +4354,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875881</v>
+        <v>119875875</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4406,21 +4401,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466957</v>
+        <v>467073</v>
       </c>
       <c r="R37" t="n">
-        <v>7052983</v>
+        <v>7053067</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4466,6 +4461,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875840</v>
+        <v>119875847</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466845</v>
+        <v>466586</v>
       </c>
       <c r="R38" t="n">
-        <v>7053062</v>
+        <v>7052711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875852</v>
+        <v>119875835</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466560</v>
+        <v>467021</v>
       </c>
       <c r="R39" t="n">
-        <v>7052408</v>
+        <v>7053255</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875874</v>
+        <v>119875839</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467066</v>
+        <v>466865</v>
       </c>
       <c r="R40" t="n">
-        <v>7053063</v>
+        <v>7053104</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875888</v>
+        <v>119875852</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466964</v>
+        <v>466560</v>
       </c>
       <c r="R3" t="n">
-        <v>7052880</v>
+        <v>7052408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875852</v>
+        <v>119875888</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466560</v>
+        <v>466964</v>
       </c>
       <c r="R4" t="n">
-        <v>7052408</v>
+        <v>7052880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875843</v>
+        <v>119875872</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466592</v>
+        <v>466957</v>
       </c>
       <c r="R27" t="n">
-        <v>7052756</v>
+        <v>7053019</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875840</v>
+        <v>119875853</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466845</v>
+        <v>466574</v>
       </c>
       <c r="R28" t="n">
-        <v>7053062</v>
+        <v>7052415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875858</v>
+        <v>119875843</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466703</v>
+        <v>466592</v>
       </c>
       <c r="R29" t="n">
-        <v>7052775</v>
+        <v>7052756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875872</v>
+        <v>119875840</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466957</v>
+        <v>466845</v>
       </c>
       <c r="R30" t="n">
-        <v>7053019</v>
+        <v>7053062</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875853</v>
+        <v>119875858</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466574</v>
+        <v>466703</v>
       </c>
       <c r="R31" t="n">
-        <v>7052415</v>
+        <v>7052775</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875886</v>
+        <v>119875883</v>
       </c>
       <c r="B2" t="n">
         <v>90580</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467236</v>
+        <v>466913</v>
       </c>
       <c r="R2" t="n">
-        <v>7053192</v>
+        <v>7053084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875852</v>
+        <v>119875842</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466560</v>
+        <v>466632</v>
       </c>
       <c r="R3" t="n">
-        <v>7052408</v>
+        <v>7052782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875888</v>
+        <v>119875876</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466964</v>
+        <v>467110</v>
       </c>
       <c r="R4" t="n">
-        <v>7052880</v>
+        <v>7053045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875881</v>
+        <v>119875856</v>
       </c>
       <c r="B5" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466957</v>
+        <v>466627</v>
       </c>
       <c r="R5" t="n">
-        <v>7052983</v>
+        <v>7052535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875884</v>
+        <v>119875860</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466925</v>
+        <v>466695</v>
       </c>
       <c r="R6" t="n">
-        <v>7052870</v>
+        <v>7052889</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875860</v>
+        <v>119875850</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1230,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466695</v>
+        <v>466550</v>
       </c>
       <c r="R7" t="n">
-        <v>7052889</v>
+        <v>7052713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875862</v>
+        <v>119875859</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1337,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466963</v>
+        <v>466682</v>
       </c>
       <c r="R8" t="n">
-        <v>7052872</v>
+        <v>7052885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875841</v>
+        <v>119875837</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1444,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466645</v>
+        <v>467009</v>
       </c>
       <c r="R9" t="n">
-        <v>7052824</v>
+        <v>7053107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875850</v>
+        <v>119875858</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1551,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466550</v>
+        <v>466703</v>
       </c>
       <c r="R10" t="n">
-        <v>7052713</v>
+        <v>7052775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875883</v>
+        <v>119875841</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466913</v>
+        <v>466645</v>
       </c>
       <c r="R11" t="n">
-        <v>7053084</v>
+        <v>7052824</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875876</v>
+        <v>119875846</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1760,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467110</v>
+        <v>466598</v>
       </c>
       <c r="R12" t="n">
-        <v>7053045</v>
+        <v>7052725</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875837</v>
+        <v>119875852</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -1867,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467009</v>
+        <v>466560</v>
       </c>
       <c r="R13" t="n">
-        <v>7053107</v>
+        <v>7052408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875856</v>
+        <v>119875836</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -1974,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466627</v>
+        <v>466991</v>
       </c>
       <c r="R14" t="n">
-        <v>7052535</v>
+        <v>7053264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875844</v>
+        <v>119875848</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2081,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466581</v>
+        <v>466583</v>
       </c>
       <c r="R15" t="n">
-        <v>7052764</v>
+        <v>7052712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875842</v>
+        <v>119875881</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466632</v>
+        <v>466957</v>
       </c>
       <c r="R17" t="n">
-        <v>7052782</v>
+        <v>7052983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875857</v>
+        <v>119875843</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2402,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466724</v>
+        <v>466592</v>
       </c>
       <c r="R18" t="n">
-        <v>7052631</v>
+        <v>7052756</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875861</v>
+        <v>119875834</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2509,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466702</v>
+        <v>467034</v>
       </c>
       <c r="R19" t="n">
-        <v>7052891</v>
+        <v>7053239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875846</v>
+        <v>119875838</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2723,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466598</v>
+        <v>466996</v>
       </c>
       <c r="R21" t="n">
-        <v>7052725</v>
+        <v>7053101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875848</v>
+        <v>119875862</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2830,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466583</v>
+        <v>466963</v>
       </c>
       <c r="R22" t="n">
-        <v>7052712</v>
+        <v>7052872</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875873</v>
+        <v>119875849</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2937,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467027</v>
+        <v>466577</v>
       </c>
       <c r="R23" t="n">
-        <v>7053077</v>
+        <v>7052711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,7 +3019,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875849</v>
+        <v>119875872</v>
       </c>
       <c r="B24" t="n">
         <v>57310</v>
@@ -3044,10 +3059,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466577</v>
+        <v>466957</v>
       </c>
       <c r="R24" t="n">
-        <v>7052711</v>
+        <v>7053019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,7 +3099,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875874</v>
+        <v>119875886</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3142,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467066</v>
+        <v>467236</v>
       </c>
       <c r="R25" t="n">
-        <v>7053063</v>
+        <v>7053192</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,11 +3202,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875882</v>
+        <v>119875884</v>
       </c>
       <c r="B26" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466607</v>
+        <v>466925</v>
       </c>
       <c r="R26" t="n">
-        <v>7052792</v>
+        <v>7052870</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875872</v>
+        <v>119875888</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466957</v>
+        <v>466964</v>
       </c>
       <c r="R27" t="n">
-        <v>7053019</v>
+        <v>7052880</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3396,11 +3406,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,7 +3432,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875853</v>
+        <v>119875847</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466574</v>
+        <v>466586</v>
       </c>
       <c r="R28" t="n">
-        <v>7052415</v>
+        <v>7052711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,7 +3539,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875843</v>
+        <v>119875853</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3574,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466592</v>
+        <v>466574</v>
       </c>
       <c r="R29" t="n">
-        <v>7052756</v>
+        <v>7052415</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875840</v>
+        <v>119875873</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466845</v>
+        <v>467027</v>
       </c>
       <c r="R30" t="n">
-        <v>7053062</v>
+        <v>7053077</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875858</v>
+        <v>119875874</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466703</v>
+        <v>467066</v>
       </c>
       <c r="R31" t="n">
-        <v>7052775</v>
+        <v>7053063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875859</v>
+        <v>119875889</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466682</v>
+        <v>466941</v>
       </c>
       <c r="R32" t="n">
-        <v>7052885</v>
+        <v>7053004</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,11 +3936,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875889</v>
+        <v>119875844</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466941</v>
+        <v>466581</v>
       </c>
       <c r="R33" t="n">
-        <v>7053004</v>
+        <v>7052764</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4038,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875836</v>
+        <v>119875875</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466991</v>
+        <v>467073</v>
       </c>
       <c r="R34" t="n">
-        <v>7053264</v>
+        <v>7053067</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875834</v>
+        <v>119875882</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467034</v>
+        <v>466607</v>
       </c>
       <c r="R35" t="n">
-        <v>7053239</v>
+        <v>7052792</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,11 +4252,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875838</v>
+        <v>119875835</v>
       </c>
       <c r="B36" t="n">
         <v>57310</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466996</v>
+        <v>467021</v>
       </c>
       <c r="R36" t="n">
-        <v>7053101</v>
+        <v>7053255</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875875</v>
+        <v>119875857</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467073</v>
+        <v>466724</v>
       </c>
       <c r="R37" t="n">
-        <v>7053067</v>
+        <v>7052631</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875847</v>
+        <v>119875839</v>
       </c>
       <c r="B38" t="n">
         <v>57310</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466586</v>
+        <v>466865</v>
       </c>
       <c r="R38" t="n">
-        <v>7052711</v>
+        <v>7053104</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875835</v>
+        <v>119875840</v>
       </c>
       <c r="B39" t="n">
         <v>57310</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467021</v>
+        <v>466845</v>
       </c>
       <c r="R39" t="n">
-        <v>7053255</v>
+        <v>7053062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875839</v>
+        <v>119875861</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466865</v>
+        <v>466702</v>
       </c>
       <c r="R40" t="n">
-        <v>7053104</v>
+        <v>7052891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875883</v>
+        <v>119875842</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466913</v>
+        <v>466632</v>
       </c>
       <c r="R2" t="n">
-        <v>7053084</v>
+        <v>7052782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875842</v>
+        <v>119875876</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466632</v>
+        <v>467110</v>
       </c>
       <c r="R3" t="n">
-        <v>7052782</v>
+        <v>7053045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875876</v>
+        <v>119875856</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467110</v>
+        <v>466627</v>
       </c>
       <c r="R4" t="n">
-        <v>7053045</v>
+        <v>7052535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875856</v>
+        <v>119875860</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466627</v>
+        <v>466695</v>
       </c>
       <c r="R5" t="n">
-        <v>7052535</v>
+        <v>7052889</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875860</v>
+        <v>119875850</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466695</v>
+        <v>466550</v>
       </c>
       <c r="R6" t="n">
-        <v>7052889</v>
+        <v>7052713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875850</v>
+        <v>119875883</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466550</v>
+        <v>466913</v>
       </c>
       <c r="R7" t="n">
-        <v>7052713</v>
+        <v>7053084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3539,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875853</v>
+        <v>119875889</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466574</v>
+        <v>466941</v>
       </c>
       <c r="R29" t="n">
-        <v>7052415</v>
+        <v>7053004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,11 +3615,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875873</v>
+        <v>119875853</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3686,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467027</v>
+        <v>466574</v>
       </c>
       <c r="R30" t="n">
-        <v>7053077</v>
+        <v>7052415</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875874</v>
+        <v>119875873</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467066</v>
+        <v>467027</v>
       </c>
       <c r="R31" t="n">
-        <v>7053063</v>
+        <v>7053077</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3828,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875889</v>
+        <v>119875874</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3871,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466941</v>
+        <v>467066</v>
       </c>
       <c r="R32" t="n">
-        <v>7053004</v>
+        <v>7053063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,6 +3931,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875844</v>
+        <v>119875882</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466581</v>
+        <v>466607</v>
       </c>
       <c r="R33" t="n">
-        <v>7052764</v>
+        <v>7052792</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,11 +4038,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875875</v>
+        <v>119875844</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467073</v>
+        <v>466581</v>
       </c>
       <c r="R34" t="n">
-        <v>7053067</v>
+        <v>7052764</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875882</v>
+        <v>119875875</v>
       </c>
       <c r="B35" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466607</v>
+        <v>467073</v>
       </c>
       <c r="R35" t="n">
-        <v>7052792</v>
+        <v>7053067</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,6 +4247,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -3539,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875889</v>
+        <v>119875853</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466941</v>
+        <v>466574</v>
       </c>
       <c r="R29" t="n">
-        <v>7053004</v>
+        <v>7052415</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,6 +3615,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3646,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875853</v>
+        <v>119875873</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466574</v>
+        <v>467027</v>
       </c>
       <c r="R30" t="n">
-        <v>7052415</v>
+        <v>7053077</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3726,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875873</v>
+        <v>119875874</v>
       </c>
       <c r="B31" t="n">
         <v>57310</v>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467027</v>
+        <v>467066</v>
       </c>
       <c r="R31" t="n">
-        <v>7053077</v>
+        <v>7053063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3833,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875874</v>
+        <v>119875889</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467066</v>
+        <v>466941</v>
       </c>
       <c r="R32" t="n">
-        <v>7053063</v>
+        <v>7053004</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3931,11 +3936,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875842</v>
+        <v>119875883</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466632</v>
+        <v>466913</v>
       </c>
       <c r="R2" t="n">
-        <v>7052782</v>
+        <v>7053084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875876</v>
+        <v>119875842</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467110</v>
+        <v>466632</v>
       </c>
       <c r="R3" t="n">
-        <v>7053045</v>
+        <v>7052782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875856</v>
+        <v>119875876</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466627</v>
+        <v>467110</v>
       </c>
       <c r="R4" t="n">
-        <v>7052535</v>
+        <v>7053045</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875860</v>
+        <v>119875856</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466695</v>
+        <v>466627</v>
       </c>
       <c r="R5" t="n">
-        <v>7052889</v>
+        <v>7052535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875850</v>
+        <v>119875860</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466550</v>
+        <v>466695</v>
       </c>
       <c r="R6" t="n">
-        <v>7052713</v>
+        <v>7052889</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875883</v>
+        <v>119875850</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466913</v>
+        <v>466550</v>
       </c>
       <c r="R7" t="n">
-        <v>7053084</v>
+        <v>7052713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875883</v>
+        <v>119875842</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466913</v>
+        <v>466632</v>
       </c>
       <c r="R2" t="n">
-        <v>7053084</v>
+        <v>7052782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875842</v>
+        <v>119875876</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466632</v>
+        <v>467110</v>
       </c>
       <c r="R3" t="n">
-        <v>7052782</v>
+        <v>7053045</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875876</v>
+        <v>119875856</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467110</v>
+        <v>466627</v>
       </c>
       <c r="R4" t="n">
-        <v>7053045</v>
+        <v>7052535</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875856</v>
+        <v>119875860</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466627</v>
+        <v>466695</v>
       </c>
       <c r="R5" t="n">
-        <v>7052535</v>
+        <v>7052889</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875860</v>
+        <v>119875850</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466695</v>
+        <v>466550</v>
       </c>
       <c r="R6" t="n">
-        <v>7052889</v>
+        <v>7052713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875850</v>
+        <v>119875883</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466550</v>
+        <v>466913</v>
       </c>
       <c r="R7" t="n">
-        <v>7052713</v>
+        <v>7053084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875882</v>
+        <v>119875844</v>
       </c>
       <c r="B33" t="n">
-        <v>90576</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466607</v>
+        <v>466581</v>
       </c>
       <c r="R33" t="n">
-        <v>7052792</v>
+        <v>7052764</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,6 +4038,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875844</v>
+        <v>119875875</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466581</v>
+        <v>467073</v>
       </c>
       <c r="R34" t="n">
-        <v>7052764</v>
+        <v>7053067</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4149,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875875</v>
+        <v>119875882</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467073</v>
+        <v>466607</v>
       </c>
       <c r="R35" t="n">
-        <v>7053067</v>
+        <v>7052792</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,11 +4252,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875842</v>
+        <v>119875883</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466632</v>
+        <v>466913</v>
       </c>
       <c r="R2" t="n">
-        <v>7052782</v>
+        <v>7053084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875876</v>
+        <v>119875849</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467110</v>
+        <v>466577</v>
       </c>
       <c r="R3" t="n">
-        <v>7053045</v>
+        <v>7052711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +887,7 @@
         <v>119875856</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875860</v>
+        <v>119875872</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466695</v>
+        <v>466957</v>
       </c>
       <c r="R5" t="n">
-        <v>7052889</v>
+        <v>7053019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875850</v>
+        <v>119875874</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466550</v>
+        <v>467066</v>
       </c>
       <c r="R6" t="n">
-        <v>7052713</v>
+        <v>7053063</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875883</v>
+        <v>119875848</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466913</v>
+        <v>466583</v>
       </c>
       <c r="R7" t="n">
-        <v>7053084</v>
+        <v>7052712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875859</v>
+        <v>119875858</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466682</v>
+        <v>466703</v>
       </c>
       <c r="R8" t="n">
-        <v>7052885</v>
+        <v>7052775</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875837</v>
+        <v>119875881</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467009</v>
+        <v>466957</v>
       </c>
       <c r="R9" t="n">
-        <v>7053107</v>
+        <v>7052983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875858</v>
+        <v>119875836</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466703</v>
+        <v>466991</v>
       </c>
       <c r="R10" t="n">
-        <v>7052775</v>
+        <v>7053264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875841</v>
+        <v>119875835</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466645</v>
+        <v>467021</v>
       </c>
       <c r="R11" t="n">
-        <v>7052824</v>
+        <v>7053255</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875846</v>
+        <v>119875847</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466598</v>
+        <v>466586</v>
       </c>
       <c r="R12" t="n">
-        <v>7052725</v>
+        <v>7052711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875852</v>
+        <v>119875861</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466560</v>
+        <v>466702</v>
       </c>
       <c r="R13" t="n">
-        <v>7052408</v>
+        <v>7052891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875836</v>
+        <v>119875834</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466991</v>
+        <v>467034</v>
       </c>
       <c r="R14" t="n">
-        <v>7053264</v>
+        <v>7053239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875848</v>
+        <v>119875862</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466583</v>
+        <v>466963</v>
       </c>
       <c r="R15" t="n">
-        <v>7052712</v>
+        <v>7052872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875851</v>
+        <v>119875845</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466560</v>
+        <v>466588</v>
       </c>
       <c r="R16" t="n">
-        <v>7052410</v>
+        <v>7052753</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875881</v>
+        <v>119875889</v>
       </c>
       <c r="B17" t="n">
-        <v>90558</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466957</v>
+        <v>466941</v>
       </c>
       <c r="R17" t="n">
-        <v>7052983</v>
+        <v>7053004</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875843</v>
+        <v>119875873</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466592</v>
+        <v>467027</v>
       </c>
       <c r="R18" t="n">
-        <v>7052756</v>
+        <v>7053077</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875834</v>
+        <v>119875882</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90594</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467034</v>
+        <v>466607</v>
       </c>
       <c r="R19" t="n">
-        <v>7053239</v>
+        <v>7052792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2555,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875845</v>
+        <v>119875875</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466588</v>
+        <v>467073</v>
       </c>
       <c r="R20" t="n">
-        <v>7052753</v>
+        <v>7053067</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875838</v>
+        <v>119875846</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466996</v>
+        <v>466598</v>
       </c>
       <c r="R21" t="n">
-        <v>7053101</v>
+        <v>7052725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875862</v>
+        <v>119875886</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466963</v>
+        <v>467236</v>
       </c>
       <c r="R22" t="n">
-        <v>7052872</v>
+        <v>7053192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,11 +2871,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875849</v>
+        <v>119875853</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466577</v>
+        <v>466574</v>
       </c>
       <c r="R23" t="n">
-        <v>7052711</v>
+        <v>7052415</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2977,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875872</v>
+        <v>119875860</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3059,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466957</v>
+        <v>466695</v>
       </c>
       <c r="R24" t="n">
-        <v>7053019</v>
+        <v>7052889</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875886</v>
+        <v>119875876</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3166,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467236</v>
+        <v>467110</v>
       </c>
       <c r="R25" t="n">
-        <v>7053192</v>
+        <v>7053045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875884</v>
+        <v>119875857</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466925</v>
+        <v>466724</v>
       </c>
       <c r="R26" t="n">
-        <v>7052870</v>
+        <v>7052631</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875888</v>
+        <v>119875852</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466964</v>
+        <v>466560</v>
       </c>
       <c r="R27" t="n">
-        <v>7052880</v>
+        <v>7052408</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875847</v>
+        <v>119875839</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466586</v>
+        <v>466865</v>
       </c>
       <c r="R28" t="n">
-        <v>7052711</v>
+        <v>7053104</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875853</v>
+        <v>119875884</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466574</v>
+        <v>466925</v>
       </c>
       <c r="R29" t="n">
-        <v>7052415</v>
+        <v>7052870</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,11 +3615,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875873</v>
+        <v>119875888</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3662,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3686,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467027</v>
+        <v>466964</v>
       </c>
       <c r="R30" t="n">
-        <v>7053077</v>
+        <v>7052880</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3722,11 +3717,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875874</v>
+        <v>119875843</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467066</v>
+        <v>466592</v>
       </c>
       <c r="R31" t="n">
-        <v>7053063</v>
+        <v>7052756</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,7 +3823,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875889</v>
+        <v>119875851</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466941</v>
+        <v>466560</v>
       </c>
       <c r="R32" t="n">
-        <v>7053004</v>
+        <v>7052410</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3936,6 +3926,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875844</v>
+        <v>119875837</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466581</v>
+        <v>467009</v>
       </c>
       <c r="R33" t="n">
-        <v>7052764</v>
+        <v>7053107</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875875</v>
+        <v>119875842</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467073</v>
+        <v>466632</v>
       </c>
       <c r="R34" t="n">
-        <v>7053067</v>
+        <v>7052782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4171,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875882</v>
+        <v>119875840</v>
       </c>
       <c r="B35" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466607</v>
+        <v>466845</v>
       </c>
       <c r="R35" t="n">
-        <v>7052792</v>
+        <v>7053062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,6 +4247,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875835</v>
+        <v>119875850</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467021</v>
+        <v>466550</v>
       </c>
       <c r="R36" t="n">
-        <v>7053255</v>
+        <v>7052713</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875857</v>
+        <v>119875838</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466724</v>
+        <v>466996</v>
       </c>
       <c r="R37" t="n">
-        <v>7052631</v>
+        <v>7053101</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875839</v>
+        <v>119875859</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466865</v>
+        <v>466682</v>
       </c>
       <c r="R38" t="n">
-        <v>7053104</v>
+        <v>7052885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875840</v>
+        <v>119875844</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466845</v>
+        <v>466581</v>
       </c>
       <c r="R39" t="n">
-        <v>7053062</v>
+        <v>7052764</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875861</v>
+        <v>119875841</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466702</v>
+        <v>466645</v>
       </c>
       <c r="R40" t="n">
-        <v>7052891</v>
+        <v>7052824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875835</v>
+        <v>119875847</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467021</v>
+        <v>466586</v>
       </c>
       <c r="R11" t="n">
-        <v>7053255</v>
+        <v>7052711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875847</v>
+        <v>119875835</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466586</v>
+        <v>467021</v>
       </c>
       <c r="R12" t="n">
-        <v>7052711</v>
+        <v>7053255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875882</v>
+        <v>119875875</v>
       </c>
       <c r="B19" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466607</v>
+        <v>467073</v>
       </c>
       <c r="R19" t="n">
-        <v>7052792</v>
+        <v>7053067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875875</v>
+        <v>119875882</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467073</v>
+        <v>466607</v>
       </c>
       <c r="R20" t="n">
-        <v>7053067</v>
+        <v>7052792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2662,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875883</v>
+        <v>119875884</v>
       </c>
       <c r="B2" t="n">
         <v>90598</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466913</v>
+        <v>466925</v>
       </c>
       <c r="R2" t="n">
-        <v>7053084</v>
+        <v>7052870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875849</v>
+        <v>119875835</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466577</v>
+        <v>467021</v>
       </c>
       <c r="R3" t="n">
-        <v>7052711</v>
+        <v>7053255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875856</v>
+        <v>119875852</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466627</v>
+        <v>466560</v>
       </c>
       <c r="R4" t="n">
-        <v>7052535</v>
+        <v>7052408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875872</v>
+        <v>119875859</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466957</v>
+        <v>466682</v>
       </c>
       <c r="R5" t="n">
-        <v>7053019</v>
+        <v>7052885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875874</v>
+        <v>119875876</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467066</v>
+        <v>467110</v>
       </c>
       <c r="R6" t="n">
-        <v>7053063</v>
+        <v>7053045</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875848</v>
+        <v>119875838</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466583</v>
+        <v>466996</v>
       </c>
       <c r="R7" t="n">
-        <v>7052712</v>
+        <v>7053101</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875858</v>
+        <v>119875882</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466703</v>
+        <v>466607</v>
       </c>
       <c r="R8" t="n">
-        <v>7052775</v>
+        <v>7052792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875881</v>
+        <v>119875848</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466957</v>
+        <v>466583</v>
       </c>
       <c r="R9" t="n">
-        <v>7052983</v>
+        <v>7052712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875836</v>
+        <v>119875844</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466991</v>
+        <v>466581</v>
       </c>
       <c r="R10" t="n">
-        <v>7053264</v>
+        <v>7052764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875847</v>
+        <v>119875872</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466586</v>
+        <v>466957</v>
       </c>
       <c r="R11" t="n">
-        <v>7052711</v>
+        <v>7053019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875835</v>
+        <v>119875888</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467021</v>
+        <v>466964</v>
       </c>
       <c r="R12" t="n">
-        <v>7053255</v>
+        <v>7052880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875861</v>
+        <v>119875874</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466702</v>
+        <v>467066</v>
       </c>
       <c r="R13" t="n">
-        <v>7052891</v>
+        <v>7053063</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875834</v>
+        <v>119875881</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467034</v>
+        <v>466957</v>
       </c>
       <c r="R14" t="n">
-        <v>7053239</v>
+        <v>7052983</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875862</v>
+        <v>119875851</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466963</v>
+        <v>466560</v>
       </c>
       <c r="R15" t="n">
-        <v>7052872</v>
+        <v>7052410</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875845</v>
+        <v>119875849</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466588</v>
+        <v>466577</v>
       </c>
       <c r="R16" t="n">
-        <v>7052753</v>
+        <v>7052711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875889</v>
+        <v>119875845</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466941</v>
+        <v>466588</v>
       </c>
       <c r="R17" t="n">
-        <v>7053004</v>
+        <v>7052753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875875</v>
+        <v>119875858</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467073</v>
+        <v>466703</v>
       </c>
       <c r="R19" t="n">
-        <v>7053067</v>
+        <v>7052775</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875882</v>
+        <v>119875834</v>
       </c>
       <c r="B20" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,21 +2597,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466607</v>
+        <v>467034</v>
       </c>
       <c r="R20" t="n">
-        <v>7052792</v>
+        <v>7053239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,6 +2657,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875846</v>
+        <v>119875836</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466598</v>
+        <v>466991</v>
       </c>
       <c r="R21" t="n">
-        <v>7052725</v>
+        <v>7053264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875886</v>
+        <v>119875875</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467236</v>
+        <v>467073</v>
       </c>
       <c r="R22" t="n">
-        <v>7053192</v>
+        <v>7053067</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,6 +2871,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875853</v>
+        <v>119875856</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466574</v>
+        <v>466627</v>
       </c>
       <c r="R23" t="n">
-        <v>7052415</v>
+        <v>7052535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875860</v>
+        <v>119875841</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466695</v>
+        <v>466645</v>
       </c>
       <c r="R24" t="n">
-        <v>7052889</v>
+        <v>7052824</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875876</v>
+        <v>119875843</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467110</v>
+        <v>466592</v>
       </c>
       <c r="R25" t="n">
-        <v>7053045</v>
+        <v>7052756</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875857</v>
+        <v>119875861</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466724</v>
+        <v>466702</v>
       </c>
       <c r="R26" t="n">
-        <v>7052631</v>
+        <v>7052891</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875852</v>
+        <v>119875840</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466560</v>
+        <v>466845</v>
       </c>
       <c r="R27" t="n">
-        <v>7052408</v>
+        <v>7053062</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,10 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875839</v>
+        <v>119875889</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466865</v>
+        <v>466941</v>
       </c>
       <c r="R28" t="n">
-        <v>7053104</v>
+        <v>7053004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,11 +3513,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875884</v>
+        <v>119875847</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466925</v>
+        <v>466586</v>
       </c>
       <c r="R29" t="n">
-        <v>7052870</v>
+        <v>7052711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,6 +3615,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875888</v>
+        <v>119875862</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3662,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466964</v>
+        <v>466963</v>
       </c>
       <c r="R30" t="n">
-        <v>7052880</v>
+        <v>7052872</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,6 +3722,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3743,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875843</v>
+        <v>119875837</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3783,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466592</v>
+        <v>467009</v>
       </c>
       <c r="R31" t="n">
-        <v>7052756</v>
+        <v>7053107</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875851</v>
+        <v>119875846</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3890,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466560</v>
+        <v>466598</v>
       </c>
       <c r="R32" t="n">
-        <v>7052410</v>
+        <v>7052725</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3930,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3957,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875837</v>
+        <v>119875883</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,21 +3983,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467009</v>
+        <v>466913</v>
       </c>
       <c r="R33" t="n">
-        <v>7053107</v>
+        <v>7053084</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4033,11 +4043,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875842</v>
+        <v>119875860</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466632</v>
+        <v>466695</v>
       </c>
       <c r="R34" t="n">
-        <v>7052782</v>
+        <v>7052889</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4149,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875840</v>
+        <v>119875850</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466845</v>
+        <v>466550</v>
       </c>
       <c r="R35" t="n">
-        <v>7053062</v>
+        <v>7052713</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875850</v>
+        <v>119875886</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466550</v>
+        <v>467236</v>
       </c>
       <c r="R36" t="n">
-        <v>7052713</v>
+        <v>7053192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,11 +4359,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875838</v>
+        <v>119875853</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466996</v>
+        <v>466574</v>
       </c>
       <c r="R37" t="n">
-        <v>7053101</v>
+        <v>7052415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875859</v>
+        <v>119875842</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466682</v>
+        <v>466632</v>
       </c>
       <c r="R38" t="n">
-        <v>7052885</v>
+        <v>7052782</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875844</v>
+        <v>119875839</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466581</v>
+        <v>466865</v>
       </c>
       <c r="R39" t="n">
-        <v>7052764</v>
+        <v>7053104</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875841</v>
+        <v>119875857</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466645</v>
+        <v>466724</v>
       </c>
       <c r="R40" t="n">
-        <v>7052824</v>
+        <v>7052631</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875884</v>
+        <v>119875859</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466925</v>
+        <v>466682</v>
       </c>
       <c r="R2" t="n">
-        <v>7052870</v>
+        <v>7052885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875835</v>
+        <v>119875837</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467021</v>
+        <v>467009</v>
       </c>
       <c r="R3" t="n">
-        <v>7053255</v>
+        <v>7053107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875852</v>
+        <v>119875849</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466560</v>
+        <v>466577</v>
       </c>
       <c r="R4" t="n">
-        <v>7052408</v>
+        <v>7052711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875859</v>
+        <v>119875847</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466682</v>
+        <v>466586</v>
       </c>
       <c r="R5" t="n">
-        <v>7052885</v>
+        <v>7052711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875876</v>
+        <v>119875886</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467110</v>
+        <v>467236</v>
       </c>
       <c r="R6" t="n">
-        <v>7053045</v>
+        <v>7053192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875838</v>
+        <v>119875889</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466996</v>
+        <v>466941</v>
       </c>
       <c r="R7" t="n">
-        <v>7053101</v>
+        <v>7053004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875882</v>
+        <v>119875856</v>
       </c>
       <c r="B8" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466607</v>
+        <v>466627</v>
       </c>
       <c r="R8" t="n">
-        <v>7052792</v>
+        <v>7052535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875848</v>
+        <v>119875857</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466583</v>
+        <v>466724</v>
       </c>
       <c r="R9" t="n">
-        <v>7052712</v>
+        <v>7052631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875844</v>
+        <v>119875876</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466581</v>
+        <v>467110</v>
       </c>
       <c r="R10" t="n">
-        <v>7052764</v>
+        <v>7053045</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875872</v>
+        <v>119875834</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466957</v>
+        <v>467034</v>
       </c>
       <c r="R11" t="n">
-        <v>7053019</v>
+        <v>7053239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875888</v>
+        <v>119875884</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466964</v>
+        <v>466925</v>
       </c>
       <c r="R12" t="n">
-        <v>7052880</v>
+        <v>7052870</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875874</v>
+        <v>119875888</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467066</v>
+        <v>466964</v>
       </c>
       <c r="R13" t="n">
-        <v>7053063</v>
+        <v>7052880</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875881</v>
+        <v>119875858</v>
       </c>
       <c r="B14" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466957</v>
+        <v>466703</v>
       </c>
       <c r="R14" t="n">
-        <v>7052983</v>
+        <v>7052775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875851</v>
+        <v>119875875</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466560</v>
+        <v>467073</v>
       </c>
       <c r="R15" t="n">
-        <v>7052410</v>
+        <v>7053067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875849</v>
+        <v>119875836</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466577</v>
+        <v>466991</v>
       </c>
       <c r="R16" t="n">
-        <v>7052711</v>
+        <v>7053264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875845</v>
+        <v>119875842</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466588</v>
+        <v>466632</v>
       </c>
       <c r="R17" t="n">
-        <v>7052753</v>
+        <v>7052782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875873</v>
+        <v>119875861</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467027</v>
+        <v>466702</v>
       </c>
       <c r="R18" t="n">
-        <v>7053077</v>
+        <v>7052891</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875858</v>
+        <v>119875883</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466703</v>
+        <v>466913</v>
       </c>
       <c r="R19" t="n">
-        <v>7052775</v>
+        <v>7053084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875834</v>
+        <v>119875882</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467034</v>
+        <v>466607</v>
       </c>
       <c r="R20" t="n">
-        <v>7053239</v>
+        <v>7052792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2652,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875836</v>
+        <v>119875850</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2728,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466991</v>
+        <v>466550</v>
       </c>
       <c r="R21" t="n">
-        <v>7053264</v>
+        <v>7052713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2758,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875875</v>
+        <v>119875839</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2835,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467073</v>
+        <v>466865</v>
       </c>
       <c r="R22" t="n">
-        <v>7053067</v>
+        <v>7053104</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875856</v>
+        <v>119875874</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2942,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466627</v>
+        <v>467066</v>
       </c>
       <c r="R23" t="n">
-        <v>7052535</v>
+        <v>7053063</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2972,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +2999,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875841</v>
+        <v>119875844</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3049,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466645</v>
+        <v>466581</v>
       </c>
       <c r="R24" t="n">
-        <v>7052824</v>
+        <v>7052764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3079,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,7 +3106,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875843</v>
+        <v>119875872</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3156,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466592</v>
+        <v>466957</v>
       </c>
       <c r="R25" t="n">
-        <v>7052756</v>
+        <v>7053019</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3186,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875861</v>
+        <v>119875852</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3263,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466702</v>
+        <v>466560</v>
       </c>
       <c r="R26" t="n">
-        <v>7052891</v>
+        <v>7052408</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3293,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875840</v>
+        <v>119875851</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3370,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466845</v>
+        <v>466560</v>
       </c>
       <c r="R27" t="n">
-        <v>7053062</v>
+        <v>7052410</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875889</v>
+        <v>119875853</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,21 +3443,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3477,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466941</v>
+        <v>466574</v>
       </c>
       <c r="R28" t="n">
-        <v>7053004</v>
+        <v>7052415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,6 +3503,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3539,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875847</v>
+        <v>119875860</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3579,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466586</v>
+        <v>466695</v>
       </c>
       <c r="R29" t="n">
-        <v>7052711</v>
+        <v>7052889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3619,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875862</v>
+        <v>119875845</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3686,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466963</v>
+        <v>466588</v>
       </c>
       <c r="R30" t="n">
-        <v>7052872</v>
+        <v>7052753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875837</v>
+        <v>119875848</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467009</v>
+        <v>466583</v>
       </c>
       <c r="R31" t="n">
-        <v>7053107</v>
+        <v>7052712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875846</v>
+        <v>119875838</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466598</v>
+        <v>466996</v>
       </c>
       <c r="R32" t="n">
-        <v>7052725</v>
+        <v>7053101</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875883</v>
+        <v>119875841</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,21 +3978,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4007,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466913</v>
+        <v>466645</v>
       </c>
       <c r="R33" t="n">
-        <v>7053084</v>
+        <v>7052824</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,6 +4038,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,7 +4069,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875860</v>
+        <v>119875843</v>
       </c>
       <c r="B34" t="n">
         <v>57320</v>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466695</v>
+        <v>466592</v>
       </c>
       <c r="R34" t="n">
-        <v>7052889</v>
+        <v>7052756</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875850</v>
+        <v>119875840</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466550</v>
+        <v>466845</v>
       </c>
       <c r="R35" t="n">
-        <v>7052713</v>
+        <v>7053062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875886</v>
+        <v>119875862</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4299,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467236</v>
+        <v>466963</v>
       </c>
       <c r="R36" t="n">
-        <v>7053192</v>
+        <v>7052872</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4359,6 +4359,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4385,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875853</v>
+        <v>119875835</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4425,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466574</v>
+        <v>467021</v>
       </c>
       <c r="R37" t="n">
-        <v>7052415</v>
+        <v>7053255</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,7 +4497,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875842</v>
+        <v>119875873</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -4532,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466632</v>
+        <v>467027</v>
       </c>
       <c r="R38" t="n">
-        <v>7052782</v>
+        <v>7053077</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4577,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875839</v>
+        <v>119875881</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4615,21 +4620,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4639,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466865</v>
+        <v>466957</v>
       </c>
       <c r="R39" t="n">
-        <v>7053104</v>
+        <v>7052983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,11 +4680,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875857</v>
+        <v>119875846</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466724</v>
+        <v>466598</v>
       </c>
       <c r="R40" t="n">
-        <v>7052631</v>
+        <v>7052725</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875859</v>
+        <v>119875851</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466682</v>
+        <v>466560</v>
       </c>
       <c r="R2" t="n">
-        <v>7052885</v>
+        <v>7052410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875837</v>
+        <v>119875850</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467009</v>
+        <v>466550</v>
       </c>
       <c r="R3" t="n">
-        <v>7053107</v>
+        <v>7052713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875849</v>
+        <v>119875886</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466577</v>
+        <v>467236</v>
       </c>
       <c r="R4" t="n">
-        <v>7052711</v>
+        <v>7053192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875847</v>
+        <v>119875882</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466586</v>
+        <v>466607</v>
       </c>
       <c r="R5" t="n">
-        <v>7052711</v>
+        <v>7052792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875886</v>
+        <v>119875848</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467236</v>
+        <v>466583</v>
       </c>
       <c r="R6" t="n">
-        <v>7053192</v>
+        <v>7052712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875889</v>
+        <v>119875853</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466941</v>
+        <v>466574</v>
       </c>
       <c r="R7" t="n">
-        <v>7053004</v>
+        <v>7052415</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875856</v>
+        <v>119875862</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466627</v>
+        <v>466963</v>
       </c>
       <c r="R8" t="n">
-        <v>7052535</v>
+        <v>7052872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875857</v>
+        <v>119875860</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466724</v>
+        <v>466695</v>
       </c>
       <c r="R9" t="n">
-        <v>7052631</v>
+        <v>7052889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875876</v>
+        <v>119875840</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467110</v>
+        <v>466845</v>
       </c>
       <c r="R10" t="n">
-        <v>7053045</v>
+        <v>7053062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875834</v>
+        <v>119875861</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467034</v>
+        <v>466702</v>
       </c>
       <c r="R11" t="n">
-        <v>7053239</v>
+        <v>7052891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875884</v>
+        <v>119875845</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466925</v>
+        <v>466588</v>
       </c>
       <c r="R12" t="n">
-        <v>7052870</v>
+        <v>7052753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875888</v>
+        <v>119875841</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466964</v>
+        <v>466645</v>
       </c>
       <c r="R13" t="n">
-        <v>7052880</v>
+        <v>7052824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875858</v>
+        <v>119875835</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466703</v>
+        <v>467021</v>
       </c>
       <c r="R14" t="n">
-        <v>7052775</v>
+        <v>7053255</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875875</v>
+        <v>119875881</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467073</v>
+        <v>466957</v>
       </c>
       <c r="R15" t="n">
-        <v>7053067</v>
+        <v>7052983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875836</v>
+        <v>119875839</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466991</v>
+        <v>466865</v>
       </c>
       <c r="R16" t="n">
-        <v>7053264</v>
+        <v>7053104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875842</v>
+        <v>119875834</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466632</v>
+        <v>467034</v>
       </c>
       <c r="R17" t="n">
-        <v>7052782</v>
+        <v>7053239</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875861</v>
+        <v>119875836</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466702</v>
+        <v>466991</v>
       </c>
       <c r="R18" t="n">
-        <v>7052891</v>
+        <v>7053264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875883</v>
+        <v>119875856</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466913</v>
+        <v>466627</v>
       </c>
       <c r="R19" t="n">
-        <v>7053084</v>
+        <v>7052535</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875882</v>
+        <v>119875859</v>
       </c>
       <c r="B20" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466607</v>
+        <v>466682</v>
       </c>
       <c r="R20" t="n">
-        <v>7052792</v>
+        <v>7052885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875850</v>
+        <v>119875872</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2718,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466550</v>
+        <v>466957</v>
       </c>
       <c r="R21" t="n">
-        <v>7052713</v>
+        <v>7053019</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875839</v>
+        <v>119875838</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2825,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466865</v>
+        <v>466996</v>
       </c>
       <c r="R22" t="n">
-        <v>7053104</v>
+        <v>7053101</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875874</v>
+        <v>119875843</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2932,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467066</v>
+        <v>466592</v>
       </c>
       <c r="R23" t="n">
-        <v>7053063</v>
+        <v>7052756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875844</v>
+        <v>119875888</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466581</v>
+        <v>466964</v>
       </c>
       <c r="R24" t="n">
-        <v>7052764</v>
+        <v>7052880</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,11 +3090,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,7 +3116,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875872</v>
+        <v>119875875</v>
       </c>
       <c r="B25" t="n">
         <v>57320</v>
@@ -3146,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466957</v>
+        <v>467073</v>
       </c>
       <c r="R25" t="n">
-        <v>7053019</v>
+        <v>7053067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,7 +3223,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875852</v>
+        <v>119875837</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3253,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466560</v>
+        <v>467009</v>
       </c>
       <c r="R26" t="n">
-        <v>7052408</v>
+        <v>7053107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,7 +3303,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875851</v>
+        <v>119875857</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3360,10 +3370,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466560</v>
+        <v>466724</v>
       </c>
       <c r="R27" t="n">
-        <v>7052410</v>
+        <v>7052631</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3437,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875853</v>
+        <v>119875849</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3467,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466574</v>
+        <v>466577</v>
       </c>
       <c r="R28" t="n">
-        <v>7052415</v>
+        <v>7052711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,7 +3517,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3544,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875860</v>
+        <v>119875876</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3574,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466695</v>
+        <v>467110</v>
       </c>
       <c r="R29" t="n">
-        <v>7052889</v>
+        <v>7053045</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875845</v>
+        <v>119875884</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3681,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466588</v>
+        <v>466925</v>
       </c>
       <c r="R30" t="n">
-        <v>7052753</v>
+        <v>7052870</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,11 +3727,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,7 +3753,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875848</v>
+        <v>119875844</v>
       </c>
       <c r="B31" t="n">
         <v>57320</v>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466583</v>
+        <v>466581</v>
       </c>
       <c r="R31" t="n">
-        <v>7052712</v>
+        <v>7052764</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3860,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875838</v>
+        <v>119875846</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466996</v>
+        <v>466598</v>
       </c>
       <c r="R32" t="n">
-        <v>7053101</v>
+        <v>7052725</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,7 +3967,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875841</v>
+        <v>119875858</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4002,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466645</v>
+        <v>466703</v>
       </c>
       <c r="R33" t="n">
-        <v>7052824</v>
+        <v>7052775</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,7 +4047,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4069,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875843</v>
+        <v>119875889</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466592</v>
+        <v>466941</v>
       </c>
       <c r="R34" t="n">
-        <v>7052756</v>
+        <v>7053004</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,11 +4150,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875840</v>
+        <v>119875852</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466845</v>
+        <v>466560</v>
       </c>
       <c r="R35" t="n">
-        <v>7053062</v>
+        <v>7052408</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,7 +4283,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875862</v>
+        <v>119875874</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466963</v>
+        <v>467066</v>
       </c>
       <c r="R36" t="n">
-        <v>7052872</v>
+        <v>7053063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875835</v>
+        <v>119875842</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467021</v>
+        <v>466632</v>
       </c>
       <c r="R37" t="n">
-        <v>7053255</v>
+        <v>7052782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875873</v>
+        <v>119875883</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467027</v>
+        <v>466913</v>
       </c>
       <c r="R38" t="n">
-        <v>7053077</v>
+        <v>7053084</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,11 +4573,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4604,10 +4599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875881</v>
+        <v>119875847</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4620,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4644,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466957</v>
+        <v>466586</v>
       </c>
       <c r="R39" t="n">
-        <v>7052983</v>
+        <v>7052711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,6 +4675,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875846</v>
+        <v>119875873</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466598</v>
+        <v>467027</v>
       </c>
       <c r="R40" t="n">
-        <v>7052725</v>
+        <v>7053077</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875851</v>
+        <v>119875847</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466560</v>
+        <v>466586</v>
       </c>
       <c r="R2" t="n">
-        <v>7052410</v>
+        <v>7052711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875850</v>
+        <v>119875888</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466550</v>
+        <v>466964</v>
       </c>
       <c r="R3" t="n">
-        <v>7052713</v>
+        <v>7052880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875886</v>
+        <v>119875843</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467236</v>
+        <v>466592</v>
       </c>
       <c r="R4" t="n">
-        <v>7053192</v>
+        <v>7052756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875882</v>
+        <v>119875858</v>
       </c>
       <c r="B5" t="n">
-        <v>90594</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466607</v>
+        <v>466703</v>
       </c>
       <c r="R5" t="n">
-        <v>7052792</v>
+        <v>7052775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875848</v>
+        <v>119875884</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466583</v>
+        <v>466925</v>
       </c>
       <c r="R6" t="n">
-        <v>7052712</v>
+        <v>7052870</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875853</v>
+        <v>119875849</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466574</v>
+        <v>466577</v>
       </c>
       <c r="R7" t="n">
-        <v>7052415</v>
+        <v>7052711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875862</v>
+        <v>119875853</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466963</v>
+        <v>466574</v>
       </c>
       <c r="R8" t="n">
-        <v>7052872</v>
+        <v>7052415</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875860</v>
+        <v>119875857</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466695</v>
+        <v>466724</v>
       </c>
       <c r="R9" t="n">
-        <v>7052889</v>
+        <v>7052631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875840</v>
+        <v>119875842</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466845</v>
+        <v>466632</v>
       </c>
       <c r="R10" t="n">
-        <v>7053062</v>
+        <v>7052782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875861</v>
+        <v>119875840</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466702</v>
+        <v>466845</v>
       </c>
       <c r="R11" t="n">
-        <v>7052891</v>
+        <v>7053062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875841</v>
+        <v>119875882</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466645</v>
+        <v>466607</v>
       </c>
       <c r="R13" t="n">
-        <v>7052824</v>
+        <v>7052792</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875835</v>
+        <v>119875886</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467021</v>
+        <v>467236</v>
       </c>
       <c r="R14" t="n">
-        <v>7053255</v>
+        <v>7053192</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875881</v>
+        <v>119875872</v>
       </c>
       <c r="B15" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,7 +2089,7 @@
         <v>466957</v>
       </c>
       <c r="R15" t="n">
-        <v>7052983</v>
+        <v>7053019</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875839</v>
+        <v>119875836</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2198,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466865</v>
+        <v>466991</v>
       </c>
       <c r="R16" t="n">
-        <v>7053104</v>
+        <v>7053264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875834</v>
+        <v>119875844</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467034</v>
+        <v>466581</v>
       </c>
       <c r="R17" t="n">
-        <v>7053239</v>
+        <v>7052764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875836</v>
+        <v>119875839</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466991</v>
+        <v>466865</v>
       </c>
       <c r="R18" t="n">
-        <v>7053264</v>
+        <v>7053104</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875856</v>
+        <v>119875883</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466627</v>
+        <v>466913</v>
       </c>
       <c r="R19" t="n">
-        <v>7052535</v>
+        <v>7053084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875859</v>
+        <v>119875846</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2626,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466682</v>
+        <v>466598</v>
       </c>
       <c r="R20" t="n">
-        <v>7052885</v>
+        <v>7052725</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875872</v>
+        <v>119875873</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2733,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466957</v>
+        <v>467027</v>
       </c>
       <c r="R21" t="n">
-        <v>7053019</v>
+        <v>7053077</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875838</v>
+        <v>119875848</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2840,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466996</v>
+        <v>466583</v>
       </c>
       <c r="R22" t="n">
-        <v>7053101</v>
+        <v>7052712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875843</v>
+        <v>119875850</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2947,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466592</v>
+        <v>466550</v>
       </c>
       <c r="R23" t="n">
-        <v>7052756</v>
+        <v>7052713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875888</v>
+        <v>119875875</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3030,21 +3020,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466964</v>
+        <v>467073</v>
       </c>
       <c r="R24" t="n">
-        <v>7052880</v>
+        <v>7053067</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,6 +3080,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875875</v>
+        <v>119875889</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467073</v>
+        <v>466941</v>
       </c>
       <c r="R25" t="n">
-        <v>7053067</v>
+        <v>7053004</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,11 +3187,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875837</v>
+        <v>119875860</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3263,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467009</v>
+        <v>466695</v>
       </c>
       <c r="R26" t="n">
-        <v>7053107</v>
+        <v>7052889</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3293,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875857</v>
+        <v>119875851</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3370,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466724</v>
+        <v>466560</v>
       </c>
       <c r="R27" t="n">
-        <v>7052631</v>
+        <v>7052410</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875849</v>
+        <v>119875861</v>
       </c>
       <c r="B28" t="n">
         <v>57320</v>
@@ -3477,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466577</v>
+        <v>466702</v>
       </c>
       <c r="R28" t="n">
-        <v>7052711</v>
+        <v>7052891</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,7 +3507,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3544,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875876</v>
+        <v>119875837</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3584,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467110</v>
+        <v>467009</v>
       </c>
       <c r="R29" t="n">
-        <v>7053045</v>
+        <v>7053107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3651,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875884</v>
+        <v>119875835</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3667,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466925</v>
+        <v>467021</v>
       </c>
       <c r="R30" t="n">
-        <v>7052870</v>
+        <v>7053255</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,6 +3717,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875844</v>
+        <v>119875881</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466581</v>
+        <v>466957</v>
       </c>
       <c r="R31" t="n">
-        <v>7052764</v>
+        <v>7052983</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,11 +3824,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3860,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875846</v>
+        <v>119875862</v>
       </c>
       <c r="B32" t="n">
         <v>57320</v>
@@ -3900,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466598</v>
+        <v>466963</v>
       </c>
       <c r="R32" t="n">
-        <v>7052725</v>
+        <v>7052872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3940,7 +3930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3967,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875858</v>
+        <v>119875859</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466703</v>
+        <v>466682</v>
       </c>
       <c r="R33" t="n">
-        <v>7052775</v>
+        <v>7052885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4047,7 +4037,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875889</v>
+        <v>119875874</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466941</v>
+        <v>467066</v>
       </c>
       <c r="R34" t="n">
-        <v>7053004</v>
+        <v>7053063</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4150,6 +4140,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4283,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875874</v>
+        <v>119875876</v>
       </c>
       <c r="B36" t="n">
         <v>57320</v>
@@ -4323,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467066</v>
+        <v>467110</v>
       </c>
       <c r="R36" t="n">
-        <v>7053063</v>
+        <v>7053045</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875842</v>
+        <v>119875856</v>
       </c>
       <c r="B37" t="n">
         <v>57320</v>
@@ -4430,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466632</v>
+        <v>466627</v>
       </c>
       <c r="R37" t="n">
-        <v>7052782</v>
+        <v>7052535</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4497,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875883</v>
+        <v>119875834</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,21 +4508,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4537,10 +4532,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466913</v>
+        <v>467034</v>
       </c>
       <c r="R38" t="n">
-        <v>7053084</v>
+        <v>7053239</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,6 +4568,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,7 +4599,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875847</v>
+        <v>119875838</v>
       </c>
       <c r="B39" t="n">
         <v>57320</v>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466586</v>
+        <v>466996</v>
       </c>
       <c r="R39" t="n">
-        <v>7052711</v>
+        <v>7053101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119875873</v>
+        <v>119875841</v>
       </c>
       <c r="B40" t="n">
         <v>57320</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467027</v>
+        <v>466645</v>
       </c>
       <c r="R40" t="n">
-        <v>7053077</v>
+        <v>7052824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119875847</v>
+        <v>119875881</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466586</v>
+        <v>466957</v>
       </c>
       <c r="R2" t="n">
-        <v>7052711</v>
+        <v>7052983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119875888</v>
+        <v>119875882</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466964</v>
+        <v>466607</v>
       </c>
       <c r="R3" t="n">
-        <v>7052880</v>
+        <v>7052792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119875843</v>
+        <v>119875888</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466592</v>
+        <v>466964</v>
       </c>
       <c r="R4" t="n">
-        <v>7052756</v>
+        <v>7052880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119875858</v>
+        <v>119875889</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466703</v>
+        <v>466941</v>
       </c>
       <c r="R5" t="n">
-        <v>7052775</v>
+        <v>7053004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119875884</v>
+        <v>119875834</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466925</v>
+        <v>467034</v>
       </c>
       <c r="R6" t="n">
-        <v>7052870</v>
+        <v>7053239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119875849</v>
+        <v>119875835</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466577</v>
+        <v>467021</v>
       </c>
       <c r="R7" t="n">
-        <v>7052711</v>
+        <v>7053255</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119875853</v>
+        <v>119875836</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466574</v>
+        <v>466991</v>
       </c>
       <c r="R8" t="n">
-        <v>7052415</v>
+        <v>7053264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1342,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,15 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119875857</v>
+        <v>119875837</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466724</v>
+        <v>467009</v>
       </c>
       <c r="R9" t="n">
-        <v>7052631</v>
+        <v>7053107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,15 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119875842</v>
+        <v>119875838</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466632</v>
+        <v>466996</v>
       </c>
       <c r="R10" t="n">
-        <v>7052782</v>
+        <v>7053101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,15 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119875840</v>
+        <v>119875839</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466845</v>
+        <v>466865</v>
       </c>
       <c r="R11" t="n">
-        <v>7053062</v>
+        <v>7053104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,15 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119875845</v>
+        <v>119875840</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466588</v>
+        <v>466845</v>
       </c>
       <c r="R12" t="n">
-        <v>7052753</v>
+        <v>7053062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,15 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119875882</v>
+        <v>119875841</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466607</v>
+        <v>466645</v>
       </c>
       <c r="R13" t="n">
-        <v>7052792</v>
+        <v>7052824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,15 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119875886</v>
+        <v>119875842</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467236</v>
+        <v>466632</v>
       </c>
       <c r="R14" t="n">
-        <v>7053192</v>
+        <v>7052782</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,15 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119875872</v>
+        <v>119875843</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466957</v>
+        <v>466592</v>
       </c>
       <c r="R15" t="n">
-        <v>7053019</v>
+        <v>7052756</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,15 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119875836</v>
+        <v>119875844</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466991</v>
+        <v>466581</v>
       </c>
       <c r="R16" t="n">
-        <v>7053264</v>
+        <v>7052764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,15 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119875844</v>
+        <v>119875845</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466581</v>
+        <v>466588</v>
       </c>
       <c r="R17" t="n">
-        <v>7052764</v>
+        <v>7052753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,15 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119875839</v>
+        <v>119875846</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466865</v>
+        <v>466598</v>
       </c>
       <c r="R18" t="n">
-        <v>7053104</v>
+        <v>7052725</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,15 +2389,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119875883</v>
+        <v>119875847</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,21 +2400,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466913</v>
+        <v>466586</v>
       </c>
       <c r="R19" t="n">
-        <v>7053084</v>
+        <v>7052711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2460,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,15 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119875846</v>
+        <v>119875848</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466598</v>
+        <v>466583</v>
       </c>
       <c r="R20" t="n">
-        <v>7052725</v>
+        <v>7052712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2566,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,15 +2593,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119875873</v>
+        <v>119875849</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467027</v>
+        <v>466577</v>
       </c>
       <c r="R21" t="n">
-        <v>7053077</v>
+        <v>7052711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2668,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack ganska färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,15 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119875848</v>
+        <v>119875850</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466583</v>
+        <v>466550</v>
       </c>
       <c r="R22" t="n">
-        <v>7052712</v>
+        <v>7052713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,15 +2797,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119875850</v>
+        <v>119875851</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,10 +2832,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466550</v>
+        <v>466560</v>
       </c>
       <c r="R23" t="n">
-        <v>7052713</v>
+        <v>7052410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,15 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119875875</v>
+        <v>119875852</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467073</v>
+        <v>466560</v>
       </c>
       <c r="R24" t="n">
-        <v>7053067</v>
+        <v>7052408</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,15 +3001,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119875889</v>
+        <v>119875853</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3012,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3036,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466941</v>
+        <v>466574</v>
       </c>
       <c r="R25" t="n">
-        <v>7053004</v>
+        <v>7052415</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3072,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,15 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119875860</v>
+        <v>119875855</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466695</v>
+        <v>466648</v>
       </c>
       <c r="R26" t="n">
-        <v>7052889</v>
+        <v>7052479</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,7 +3178,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3320,15 +3205,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119875851</v>
+        <v>119875856</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3360,10 +3240,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466560</v>
+        <v>466627</v>
       </c>
       <c r="R27" t="n">
-        <v>7052410</v>
+        <v>7052535</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,15 +3307,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119875861</v>
+        <v>119875857</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3467,10 +3342,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466702</v>
+        <v>466724</v>
       </c>
       <c r="R28" t="n">
-        <v>7052891</v>
+        <v>7052631</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,15 +3409,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119875837</v>
+        <v>119875858</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467009</v>
+        <v>466703</v>
       </c>
       <c r="R29" t="n">
-        <v>7053107</v>
+        <v>7052775</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,15 +3511,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119875835</v>
+        <v>119875859</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3681,10 +3546,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467021</v>
+        <v>466682</v>
       </c>
       <c r="R30" t="n">
-        <v>7053255</v>
+        <v>7052885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3586,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,15 +3613,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119875881</v>
+        <v>119875860</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,21 +3624,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466957</v>
+        <v>466695</v>
       </c>
       <c r="R31" t="n">
-        <v>7052983</v>
+        <v>7052889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3684,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,15 +3715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119875862</v>
+        <v>119875861</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466963</v>
+        <v>466702</v>
       </c>
       <c r="R32" t="n">
-        <v>7052872</v>
+        <v>7052891</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,15 +3817,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119875859</v>
+        <v>119875862</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3997,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466682</v>
+        <v>466963</v>
       </c>
       <c r="R33" t="n">
-        <v>7052885</v>
+        <v>7052872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4037,7 +3892,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,15 +3919,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119875874</v>
+        <v>119875872</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4104,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467066</v>
+        <v>466957</v>
       </c>
       <c r="R34" t="n">
-        <v>7053063</v>
+        <v>7053019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +3994,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,15 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119875852</v>
+        <v>119875873</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4211,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466560</v>
+        <v>467027</v>
       </c>
       <c r="R35" t="n">
-        <v>7052408</v>
+        <v>7053077</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4251,7 +4096,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,15 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119875876</v>
+        <v>119875874</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467110</v>
+        <v>467066</v>
       </c>
       <c r="R36" t="n">
-        <v>7053045</v>
+        <v>7053063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,15 +4225,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119875856</v>
+        <v>119875875</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466627</v>
+        <v>467073</v>
       </c>
       <c r="R37" t="n">
-        <v>7052535</v>
+        <v>7053067</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4465,7 +4300,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4492,15 +4327,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119875834</v>
+        <v>119875876</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4532,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467034</v>
+        <v>467110</v>
       </c>
       <c r="R38" t="n">
-        <v>7053239</v>
+        <v>7053045</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,7 +4402,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4599,15 +4429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119875838</v>
+        <v>119875877</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4639,10 +4464,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466996</v>
+        <v>467236</v>
       </c>
       <c r="R39" t="n">
-        <v>7053101</v>
+        <v>7053152</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,113 +4528,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>119875841</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Sandlingsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>466645</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7052824</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35749-2024 artfynd.xlsx
+++ b/artfynd/A 35749-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875881</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875882</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875888</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875834</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875835</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875836</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875837</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875838</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875839</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875840</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875841</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875842</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2080,6 +2150,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875843</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2182,6 +2257,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875844</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875845</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875846</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2488,6 +2578,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875847</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2590,6 +2685,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875848</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875849</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875850</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875851</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2998,6 +3113,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875852</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875853</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3202,6 +3327,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875855</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3304,6 +3434,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875856</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3406,6 +3541,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875857</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3508,6 +3648,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875858</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3610,6 +3755,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875859</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875860</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3814,6 +3969,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875861</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3916,6 +4076,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875862</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4018,6 +4183,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875872</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4120,6 +4290,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875873</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4222,6 +4397,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875874</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875875</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4426,6 +4611,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875876</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4528,8 +4718,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119875877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>